--- a/projects/auto_page/autopageMKII/tables/Accel_mode2.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode2.xlsx
@@ -11,7 +11,11 @@
     <sheet name="Failed_Orders" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Completed_Orders" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$624</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Failed_Orders'!$A$1:$C$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Completed_Orders'!$A$1:$E$674</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -4874,6 +4878,7 @@
       <c r="B624" s="6" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B624"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4905,522 +4910,522 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>260628A13KF904</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>ไม่พบออเดอร์ 260628A13KF904 ในระบบ Shopee หรือค้นหาไม่สำเร็จ (ด่านที่ติด: เริ่มรัน)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 13:21:47</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>260630E55EPY52</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000646 (วันที่: 2026-06-30 09:43, ราคาที่ต้องออกบิล: 4466.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:05:58</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>260630E581MKYC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000646 (วันที่: 2026-06-30 09:44, ราคาที่ต้องออกบิล: 4466.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:06:12</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>260630E5K978VQ</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000646 (วันที่: 2026-06-30 09:50, ราคาที่ต้องออกบิล: 4466.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:06:27</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>260630EBN9KJ8V</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-06-30 11:39, ราคาที่ต้องออกบิล: 2803.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:06:48</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>260630EDA9843T</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000677 (วันที่: 2026-06-30 12:09, ราคาที่ต้องออกบิล: 4002.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:07:02</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>260630EJS3FUVW</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000646 (วันที่: 2026-06-30 13:46, ราคาที่ต้องออกบิล: 4466.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:07:16</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>260630EK4Y3XUR</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000646 (วันที่: 2026-06-30 13:53, ราคาที่ต้องออกบิล: 4466.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:07:30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>260630EK69YG4U</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-06-30 13:54, ราคาที่ต้องออกบิล: 2803.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:07:49</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>260630EMJPYT1M</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000677 (วันที่: 2026-06-30 14:18, ราคาที่ต้องออกบิล: 4002.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:08:03</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>260630EN3Y47M1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002481 (วันที่: 2026-06-30 14:28, ราคาที่ต้องออกบิล: 6688.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:08:19</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>260630ES5W5BCX</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR6-000436 (วันที่: 2026-06-30 15:41, ราคาที่ต้องออกบิล: 11008.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:08:30</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>260630EWJT3DHY</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000631 (วันที่: 2026-06-30 17:00, ราคาที่ต้องออกบิล: 1290.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:08:50</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>260630EX8Q2MFQ</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-06-30 17:12, ราคาที่ต้องออกบิล: 2803.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:09:06</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>260630F51VFESE</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-06-30 19:13, ราคาที่ต้องออกบิล: 2803.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:09:27</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>260630F7PWBQ50</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-06-30 20:01, ราคาที่ต้องออกบิล: 2803.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:09:43</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>260630F9D6X502</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002497 (วันที่: 2026-06-30 20:31, ราคาที่ต้องออกบิล: 3645.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:09:58</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>260701H8DRBHWH</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002387 (วันที่: 2026-07-01 15:19, ราคาที่ต้องออกบิล: 2871.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:18:42</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>260701H8FCU5UW</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001753+SP2-001755 (วันที่: 2026-07-01 15:20, ราคาที่ต้องออกบิล: 1070.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:19:00</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>260701HAF1TU0B</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002387 (วันที่: 2026-07-01 15:55, ราคาที่ต้องออกบิล: 2871.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:21:19</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>260701HGHU3DNK</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001778+SP2-001779 (วันที่: 2026-07-01 17:44, ราคาที่ต้องออกบิล: 860.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:28:28</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>260701HGVKA8P8</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: VD3-000242 (วันที่: 2026-07-01 17:50, ราคาที่ต้องออกบิล: 587.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:29:09</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>260701HP8VHUSU</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: IP2-000242 (วันที่: 2026-07-01 19:27, ราคาที่ต้องออกบิล: 3159.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:33:28</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>260701HQCXGDWC</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002387 (วันที่: 2026-07-01 19:47, ราคาที่ต้องออกบิล: 2871.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:34:56</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>260701J0AGMH5J</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001753+SP2-001755 (วันที่: 2026-07-01 22:27, ราคาที่ต้องออกบิล: 1070.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:43:31</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>260702J2D09D6H</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: IP4-002384 (วันที่: 2026-07-01 23:04, ราคาที่ต้องออกบิล: 109.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:45:53</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>260702J7JPPYNQ</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002400 (วันที่: 2026-07-02 00:36, ราคาที่ต้องออกบิล: 5730.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:49:53</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>260702J911NQFH</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002229 (วันที่: 2026-07-02 01:02, ราคาที่ต้องออกบิล: 2541.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 14:50:56</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>260702K8X97TK8</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>ไม่พบออเดอร์ 260702K8X97TK8 ในระบบ Shopee หรือค้นหาไม่สำเร็จ (ด่านที่ติด: เริ่มรัน)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:01:03</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>260702K9FVUPY0</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-07-02 10:43, ราคาที่ต้องออกบิล: 2784.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:01:35</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>260702KA1VUS3W</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Postal code 10130 cannot be found in dropdown, auto invoice mode requires postal code selection, stopping the process. Error details: Message: no such element: Unable to locate element: {"method":"xpath","selector":"//li[@role='treeitem' and text()='10130']"}
   (Session info: chrome=150.0.7871.47); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
@@ -5447,19 +5452,19 @@
  (ด่านที่ติด: ใส่ชื่อลูกค้าสำเร็จ)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:02:42</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>260702KAD4D1K2</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Postal code 10320 cannot be found in dropdown, auto invoice mode requires postal code selection, stopping the process. Error details: Message: no such element: Unable to locate element: {"method":"xpath","selector":"//li[@role='treeitem' and text()='10320']"}
   (Session info: chrome=150.0.7871.47); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
@@ -5486,444 +5491,444 @@
  (ด่านที่ติด: ใส่ชื่อลูกค้าสำเร็จ)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:03:24</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>260702KG5GQVXR</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: IP2-000384 (วันที่: 2026-07-02 12:43, ราคาที่ต้องออกบิล: 13595.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:18:47</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>260702KJBPPA2A</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001696+SP2-001697+SP2-001698+SP2-001699 (วันที่: 2026-07-02 13:22, ราคาที่ต้องออกบิล: 1487.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:24:13</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>260702KJBQKNA3</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000668 (วันที่: 2026-07-02 13:22, ราคาที่ต้องออกบิล: 4540.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:24:35</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>260702KJW5G1AN</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR6-000436 (วันที่: 2026-07-02 13:32, ราคาที่ต้องออกบิล: 10896.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:26:08</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>260702KJXYPHVW</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-07-02 13:33, ราคาที่ต้องออกบิล: 958.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:27:14</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>260702KKG4YS81</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001753+SP2-001755 (วันที่: 2026-07-02 13:42, ราคาที่ต้องออกบิล: 962.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:28:45</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>260702KKHF07SK</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP4-000241 (วันที่: 2026-07-02 13:43, ราคาที่ต้องออกบิล: 375.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:28:57</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>260702KKN2B28E</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000658 (วันที่: 2026-07-02 13:45, ราคาที่ต้องออกบิล: 3404.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:29:08</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>260702KM33J5N7</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-07-02 13:53, ราคาที่ต้องออกบิล: 951.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:30:19</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>260702KMBQ4T5X</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001845+SP2-001846+SP2-001847+SP2-001848 (วันที่: 2026-07-02 13:58, ราคาที่ต้องออกบิล: 951.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:31:08</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>260702KMTCANPT</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP4-000302 (วันที่: 2026-07-02 14:06, ราคาที่ต้องออกบิล: 139.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:33:40</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>260702KN2MJC1N</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001696+SP2-001697+SP2-001698+SP2-001699 (วันที่: 2026-07-02 14:11, ราคาที่ต้องออกบิล: 1487.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:34:51</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>260702KNB68JU5</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000658 (วันที่: 2026-07-02 14:16, ราคาที่ต้องออกบิล: 3404.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:35:44</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>260702KNE0UU9N</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000658 (วันที่: 2026-07-02 14:17, ราคาที่ต้องออกบิล: 3404.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:36:13</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>260702KNUSF4GF</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000658 (วันที่: 2026-07-02 14:25, ราคาที่ต้องออกบิล: 3404.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:37:03</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>260702KNVDFKPV</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000658 (วันที่: 2026-07-02 14:25, ราคาที่ต้องออกบิล: 3404.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:37:16</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>260702KPBE2BCA</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000658 (วันที่: 2026-07-02 14:34, ราคาที่ต้องออกบิล: 3404.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:39:15</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>260702KPDGUG8A</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-07-02 14:35, ราคาที่ต้องออกบิล: 958.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:39:36</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>260702KPDNNQVF</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: IP4-002384 (วันที่: 2026-07-02 14:35, ราคาที่ต้องออกบิล: 109.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:39:53</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>260702KPUQT5DA</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000646 (วันที่: 2026-07-02 14:43, ราคาที่ต้องออกบิล: 4540.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:40:33</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>260702KQ349DA2</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP4-000241 (วันที่: 2026-07-02 14:47, ราคาที่ต้องออกบิล: 375.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 15:41:32</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>260702KRMAT04G</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001703+SP2-001596+SP2-001597+SP2-001598 (วันที่: 2026-07-02 15:14, ราคาที่ต้องออกบิล: 958.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 16:45:40</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>260702KRUT6CES</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: IP7-000928 (วันที่: 2026-07-02 15:18, ราคาที่ต้องออกบิล: 268.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 16:45:57</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>260702KTN25A7M</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP4-000196 (วันที่: 2026-07-02 15:50, ราคาที่ต้องออกบิล: 308.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 16:49:46</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>260702KTXKACRP</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001753+SP2-001755 (วันที่: 2026-07-02 15:56, ราคาที่ต้องออกบิล: 962.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 16:50:02</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>260703MY6DF96D</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>Message: stale element reference: stale element not found in the current frame
   (Session info: chrome=150.0.7871.47); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#stale-element-reference-exception
@@ -5955,971 +5960,971 @@
  (ด่านที่ติด: เริ่มรัน)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:00:28</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>260703NB5HXF2Q</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Auto Invoice Mode is ON, but failed to add customer. Error: Popup not found after adding customer. (ด่านที่ติด: เริ่มรัน)</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:08:07</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>260701H28B703S</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: IP4-002195 (วันที่: 2026-07-01 13:29, ราคาที่ต้องออกบิล: 184.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:16:41</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>260701H4N20UQ1</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-07-01 14:11, ราคาที่ต้องออกบิล: 2784.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:16:59</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>260701H59N0BQ4</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-07-01 14:23, ราคาที่ต้องออกบิล: 2784.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:17:17</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>260701HGY4E4U6</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-07-01 17:52, ราคาที่ต้องออกบิล: 2784.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:17:52</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>260701HJ3MM4X5</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-07-01 18:12, ราคาที่ต้องออกบิล: 2784.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:18:12</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>260702JDJN9B0D</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002229 (วันที่: 2026-07-02 02:24, ราคาที่ต้องออกบิล: 2541.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:19:25</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>260702JS1QPGRR</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002261 (วันที่: 2026-07-02 05:49, ราคาที่ต้องออกบิล: 9643.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:19:47</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>260702KAWPMNXN</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002457 (วันที่: 2026-07-02 11:09, ราคาที่ต้องออกบิล: 5324.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:20:38</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>260702KH7D1PW2</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-07-02 13:02, ราคาที่ต้องออกบิล: 1334.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:21:20</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>260702KJWGXYXQ</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002229 (วันที่: 2026-07-02 13:32, ราคาที่ต้องออกบิล: 2541.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:21:52</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>260702KM61Y7WQ</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000582 (วันที่: 2026-07-02 13:55, ราคาที่ต้องออกบิล: 2293.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:22:28</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>260702KMPQYBN3</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-07-02 14:04, ราคาที่ต้องออกบิล: 1183.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:22:58</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>260702KN2HNN9P</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000611 (วันที่: 2026-07-02 14:11, ราคาที่ต้องออกบิล: 5017.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:23:15</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>260702KP0G4AFV</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000610 (วันที่: 2026-07-02 14:27, ราคาที่ต้องออกบิล: 4427.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:24:04</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>260702KP5M4KXQ</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-07-02 14:30, ราคาที่ต้องออกบิล: 1183.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:24:29</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>260702KQ4MWHQ7</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR2-000496 (วันที่: 2026-07-02 14:48, ราคาที่ต้องออกบิล: 3780.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:25:15</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>260702KQQAUQDE</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002270 (วันที่: 2026-07-02 14:58, ราคาที่ต้องออกบิล: 3391.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:25:36</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>260702KU9J8HJU</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: IP4-002274 (วันที่: 2026-07-02 16:02, ราคาที่ต้องออกบิล: 323.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:27:02</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>260702KVUDS34Y</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR2-000496 (วันที่: 2026-07-02 16:30, ราคาที่ต้องออกบิล: 3780.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:27:31</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>260702KWQSPW2M</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000658 (วันที่: 2026-07-02 16:46, ราคาที่ต้องออกบิล: 3404.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:27:59</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>260702KX9YD9QJ</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-07-02 16:56, ราคาที่ต้องออกบิล: 1334.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:28:21</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>260702KYPVMVQW</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-07-02 17:21, ราคาที่ต้องออกบิล: 1183.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:29:21</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>260702M1DPCTPV</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002085 (วันที่: 2026-07-02 17:52, ราคาที่ต้องออกบิล: 8565.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:30:18</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>260702M1G6GBMD</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002085 (วันที่: 2026-07-02 17:53, ราคาที่ต้องออกบิล: 8565.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:30:43</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>260702M3BQ093G</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR2-000495 (วันที่: 2026-07-02 18:26, ราคาที่ต้องออกบิล: 4143.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:31:46</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>260702M4XWF8T3</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-07-02 18:55, ราคาที่ต้องออกบิล: 1334.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:32:19</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>260702M7D5RFAM</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-07-02 19:39, ราคาที่ต้องออกบิล: 1183.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:33:36</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>260702M7P6QBT2</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-07-02 19:44, ราคาที่ต้องออกบิล: 1334.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:34:13</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>260702MAHEW9K0</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000611 (วันที่: 2026-07-02 20:35, ราคาที่ต้องออกบิล: 5017.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:35:23</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>260702MDTQ8191</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000658 (วันที่: 2026-07-02 21:34, ราคาที่ต้องออกบิล: 3404.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:36:36</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>260702MFU8WJ6J</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000673 (วันที่: 2026-07-02 22:10, ราคาที่ต้องออกบิล: 7173.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:37:14</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>260702MHJNTKQ1</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-07-02 22:41, ราคาที่ต้องออกบิล: 1183.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:37:44</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>260703MJP4Q6HY</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002270 (วันที่: 2026-07-02 23:01, ราคาที่ต้องออกบิล: 3391.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:38:20</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>260703MKTK16VB</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO2-003765 (วันที่: 2026-07-02 23:21, ราคาที่ต้องออกบิล: 20454.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:38:47</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>260703MN5H9CVD</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-07-02 23:45, ราคาที่ต้องออกบิล: 1183.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:39:22</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>260703MN6C103Y</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002387 (วันที่: 2026-07-02 23:45, ราคาที่ต้องออกบิล: 2871.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:39:38</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>260703NBFCNCT8</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001792+SP2-001793+SP2-001794+SP2-001795 (วันที่: 2026-07-03 06:24, ราคาที่ต้องออกบิล: 1334.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:41:56</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>260703NM8GPE73</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000582 (วันที่: 2026-07-03 09:01, ราคาที่ต้องออกบิล: 2293.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:46:46</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>260703NN8HUY72</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR6-000223 (วันที่: 2026-07-03 09:19, ราคาที่ต้องออกบิล: 4200.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:47:24</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>260703NP2HG2PW</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO6-011444 (วันที่: 2026-07-03 09:34, ราคาที่ต้องออกบิล: 20415.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:48:41</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>260703NP9EP24G</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000627 (วันที่: 2026-07-03 09:38, ราคาที่ต้องออกบิล: 3042.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:49:10</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>260703NPBMA95M</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000580 (วันที่: 2026-07-03 09:39, ราคาที่ต้องออกบิล: 6946.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:49:22</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>260703NPY5YTQP</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000645 (วันที่: 2026-07-03 09:50, ราคาที่ต้องออกบิล: 3961.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:50:43</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>260703NQUKPXJP</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001610+SP2-001611+SP2-001612+SP2-001613 (วันที่: 2026-07-03 10:06, ราคาที่ต้องออกบิล: 1183.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:52:25</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>260703NS5WYHBJ</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR2-000496 (วันที่: 2026-07-03 10:29, ราคาที่ต้องออกบิล: 3780.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:55:20</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>260703NS77WF4C</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000582 (วันที่: 2026-07-03 10:30, ราคาที่ต้องออกบิล: 2293.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:55:44</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>260703NSM2XR7D</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000627 (วันที่: 2026-07-03 10:37, ราคาที่ต้องออกบิล: 3042.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 19:56:11</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>260703NUV7T6UB</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001778+SP2-001779 (วันที่: 2026-07-03 11:18, ราคาที่ต้องออกบิล: 825.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 20:00:49</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>260703NV4UDAYK</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000610 (วันที่: 2026-07-03 11:23, ราคาที่ต้องออกบิล: 4427.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 20:01:15</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>260703NVE7UHRU</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO6-011444 (วันที่: 2026-07-03 11:28, ราคาที่ต้องออกบิล: 20415.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 20:01:37</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>260703NW5WXRSG</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000574 (วันที่: 2026-07-03 11:41, ราคาที่ต้องออกบิล: 6526.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 20:02:34</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>260703NW83K66M</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000627 (วันที่: 2026-07-03 11:42, ราคาที่ต้องออกบิล: 3042.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 20:02:58</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>260703NXBYTPU0</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000646 (วันที่: 2026-07-03 12:02, ราคาที่ต้องออกบิล: 4540.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 20:04:25</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>260703P01PCCKM</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000646 (วันที่: 2026-07-03 12:32, ราคาที่ต้องออกบิล: 4540.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 20:06:20</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>260701FKSXQN8P</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-06-30 23:37, ราคาที่ต้องออกบิล: 2803.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 20:11:32</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>260701GSPW9791</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>Message: no such element: Unable to locate element: {"method":"xpath","selector":"/html/body/div[2]/div[3]/div[13]/span/span/span[2]/ul/li[2]"}
   (Session info: chrome=150.0.7871.47); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
@@ -6946,19 +6951,19 @@
  (ด่านที่ติด: เริ่มรัน)</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>2026-07-03 20:11:44</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>260704REUWPPNG</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>Message: no such element: element not found
   (Session info: chrome=149.0.7827.54); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
@@ -6990,591 +6995,592 @@
  (ด่านที่ติด: เริ่มรัน)</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 12:15:31</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>260701GXEU4KEQ</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002306 (วันที่: 2026-07-01 12:21, ราคาที่ต้องออกบิล: 7376.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 15:51:17</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>260702J32DYJAN</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002120 (วันที่: 2026-07-01 23:16, ราคาที่ต้องออกบิล: 6501.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C119" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 15:52:53</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="6" t="inlineStr">
         <is>
           <t>260702KEAQ6FYH</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: IP2-000241 (วันที่: 2026-07-02 12:10, ราคาที่ต้องออกบิล: 2598.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 15:55:01</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>260702KNA8MXFQ</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: IP2-000241 (วันที่: 2026-07-02 14:15, ราคาที่ต้องออกบิล: 2598.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 15:55:17</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>260702KR244QTE</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO6-011418 (วันที่: 2026-07-02 15:04, ราคาที่ต้องออกบิล: 28190.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 15:55:34</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>260702KYN2G2XE</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO6-011655 (วันที่: 2026-07-02 17:20, ราคาที่ต้องออกบิล: 39190.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C123" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 15:56:49</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>260702M7YTT1VF</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO6-011418 (วันที่: 2026-07-02 19:49, ราคาที่ต้องออกบิล: 28190.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 15:58:21</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>260702MAKY0CEJ</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO6-011656 (วันที่: 2026-07-02 20:36, ราคาที่ต้องออกบิล: 38690.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 15:58:36</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t>260703NQBRBUR7</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002399 (วันที่: 2026-07-03 09:57, ราคาที่ต้องออกบิล: 11297.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:01:08</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>260703NY0B7YAD</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP1-000908 (วันที่: 2026-07-03 12:14, ราคาที่ต้องออกบิล: 2029.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:02:01</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>260703NY279VJ5</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000673 (วันที่: 2026-07-03 12:15, ราคาที่ต้องออกบิล: 7173.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:02:20</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>260703P925WHJV</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: SP2-001799+SP2-001800+SP2-001801+SP2-001802 (วันที่: 2026-07-03 15:14, ราคาที่ต้องออกบิล: 1847.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:04:18</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>260703PK6852QF</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: AC2-001562 (วันที่: 2026-07-03 18:15, ราคาที่ต้องออกบิล: 1177.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:05:51</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>260703PV8PPGJ0</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO6-011418 (วันที่: 2026-07-03 20:57, ราคาที่ต้องออกบิล: 28190.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:06:23</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>260703Q26MFG8P</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO6-011418 (วันที่: 2026-07-03 22:44, ราคาที่ต้องออกบิล: 28190.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:06:52</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>260704QDMHMG2J</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO6-011418 (วันที่: 2026-07-04 02:08, ราคาที่ต้องออกบิล: 28190.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:08:03</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>260704R5NTU0CX</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002085 (วันที่: 2026-07-04 09:18, ราคาที่ต้องออกบิล: 8565.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:09:57</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="6" t="inlineStr">
         <is>
           <t>260704R8MB0KBW</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002229 (วันที่: 2026-07-04 10:11, ราคาที่ต้องออกบิล: 2541.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:12:05</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>260704RBJFNJ77</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR6-000453 (วันที่: 2026-07-04 11:04, ราคาที่ต้องออกบิล: 12201.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:13:34</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>260704RDFX282P</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>ไม่พบออเดอร์ 260704RDFX282P ในระบบ Shopee หรือค้นหาไม่สำเร็จ (ด่านที่ติด: เริ่มรัน)</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:14:08</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>260704RRHGHEBN</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000683 (วันที่: 2026-07-04 14:56, ราคาที่ต้องออกบิล: 1759.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:18:07</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="6" t="inlineStr">
         <is>
           <t>260704RWQN7GD9</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR6-000223 (วันที่: 2026-07-04 16:29, ราคาที่ต้องออกบิล: 4200.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C139" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:20:05</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="6" t="inlineStr">
         <is>
           <t>260704S0G3QDFA</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B140" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002435 (วันที่: 2026-07-04 17:18, ราคาที่ต้องออกบิล: 2784.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C140" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:21:10</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="6" t="inlineStr">
         <is>
           <t>260704S28TKMX9</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002229 (วันที่: 2026-07-04 17:50, ราคาที่ต้องออกบิล: 2541.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C141" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:22:03</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="6" t="inlineStr">
         <is>
           <t>260704S2PRWCHQ</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000655 (วันที่: 2026-07-04 17:58, ราคาที่ต้องออกบิล: 8399.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C142" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:22:25</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="6" t="inlineStr">
         <is>
           <t>260704S3B909K3</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PR5-000658 (วันที่: 2026-07-04 18:09, ราคาที่ต้องออกบิล: 3404.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C143" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:23:09</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="6" t="inlineStr">
         <is>
           <t>260704S4N12RAW</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002229 (วันที่: 2026-07-04 18:33, ราคาที่ต้องออกบิล: 2541.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C144" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:23:31</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>260704S78CHUSM</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B145" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002281 (วันที่: 2026-07-04 19:19, ราคาที่ต้องออกบิล: 20272.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C145" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:24:22</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="6" t="inlineStr">
         <is>
           <t>260704S9X91NRW</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO6-011656 (วันที่: 2026-07-04 20:08, ราคาที่ต้องออกบิล: 38690.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:26:20</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="6" t="inlineStr">
         <is>
           <t>260704SBGJT87C</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: PW5-000245 (วันที่: 2026-07-04 20:36, ราคาที่ต้องออกบิล: 1077.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C147" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:27:48</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="6" t="inlineStr">
         <is>
           <t>260704SBMW3BEM</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: MNL-002281 (วันที่: 2026-07-04 20:38, ราคาที่ต้องออกบิล: 20272.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C148" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:28:18</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t>260704SKETNUP9</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B149" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: AC2-001562 (วันที่: 2026-07-04 22:58, ราคาที่ต้องออกบิล: 1177.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C149" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:33:05</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="6" t="inlineStr">
         <is>
           <t>260705SM20T1DK</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B150" s="6" t="inlineStr">
         <is>
           <t>Order skipped, CP/DC not found for SKU: CO6-011681 (วันที่: 2026-07-04 23:08, ราคาที่ต้องออกบิล: 43590.0) (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C150" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:33:35</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="6" t="inlineStr">
         <is>
           <t>260705SRFD1KJB</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>ไม่พบออเดอร์ 260705SRFD1KJB ในระบบ Shopee หรือค้นหาไม่สำเร็จ (ด่านที่ติด: เริ่มรัน)</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C151" s="6" t="inlineStr">
         <is>
           <t>2026-07-06 16:35:45</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20403,6 +20409,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E674"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>